--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1529,6 +1529,135 @@
       <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122424893</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137184382</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Orrmossen, Simonstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>561339</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6516867</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tjädertupp som stod i vägkanten. Stannade bilen, då sprang den och sedan flög den iväg. I närheten av där jag såg en död tjädertupp för 1 år sedan.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofia Hallström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sofia Hallström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137184382</t>
         </is>
       </c>
     </row>
@@ -1542,6 +1671,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>137184382</v>
       </c>
       <c r="B10" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>137184382</v>
       </c>
       <c r="B10" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -1568,11 +1568,7 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>137184382</v>
       </c>
       <c r="B10" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>137184382</v>
       </c>
       <c r="B10" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>137184382</v>
       </c>
       <c r="B10" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
